--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,10 +498,8 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6222021234567890</t>
-        </is>
+      <c r="E2" t="n">
+        <v>6222021234567890</v>
       </c>
       <c r="F2" t="n">
         <v>-1000</v>
@@ -523,6 +521,194 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>TXN001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260611104340437947f88b181c5262465483e75e1378b8900f</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京银行</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1090312345678901</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>采购付款</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>供应商A公司</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BJ20240105001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>202606111043404379790216b354c7c64703a6fe1572d1762816</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京银行</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1090312345678901</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>客户B公司</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BJ20240110002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>202606111044598830259d5bfccbb2cc46e2aa136cf6f11aec4c</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>东亚银行</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>38812345678</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>上海YY贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>向 张三 付款-货款</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>向 张三 付款-货款</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>480000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>EA20240103001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260611104459883066df7e1a9187d149c49b206b0dceab6dd2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>东亚银行</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38812345678</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>上海YY贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>收到 李四 汇款-服务费</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>收到 李四 汇款-服务费</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>515000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>EA20240108002</t>
         </is>
       </c>
     </row>

--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026061109315983702333ec6864af7846dfa4a7902365bf3d3f</t>
+          <t>20260611113056910788fe5bd5ec6ae2476785765548ec59ff95</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,38 +496,46 @@
           <t>北京银行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>6222021234567890</v>
+      <c r="C2" t="n">
+        <v>1090312345678901</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>-1000</v>
+        <v>-50000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>测试交易</t>
+          <t>采购付款</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>供应商A公司</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5000</v>
+        <v>1500000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TXN001</t>
+          <t>BJ20240105001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260611104340437947f88b181c5262465483e75e1378b8900f</t>
+          <t>20260611113056910982d11b53259d0c4061a0260aaa6b2b82c0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -545,36 +553,36 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>-50000</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>80000</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>采购付款</t>
+          <t>销售收款</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>供应商A公司</t>
+          <t>客户B公司</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1500000</v>
+        <v>1580000</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>BJ20240105001</t>
+          <t>BJ20240110002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>202606111043404379790216b354c7c64703a6fe1572d1762816</t>
+          <t>2026061111305702175435f5906dcf714198850584d2215db29b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -582,8 +590,10 @@
           <t>北京银行</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>1090312345678901</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>01090312345678901</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -592,123 +602,29 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>80000</v>
+        <v>10000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>销售收款</t>
+          <t>测试收款</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>客户B公司</t>
+          <t>测试公司</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1580000</v>
+        <v>10000</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>BJ20240110002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>202606111044598830259d5bfccbb2cc46e2aa136cf6f11aec4c</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>东亚银行</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>38812345678</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>上海YY贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2024-01-03</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>向 张三 付款-货款</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>向 张三 付款-货款</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>480000</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>EA20240103001</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20260611104459883066df7e1a9187d149c49b206b0dceab6dd2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>东亚银行</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>38812345678</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>上海YY贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024-01-08</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>35000</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>收到 李四 汇款-服务费</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>收到 李四 汇款-服务费</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>515000</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>EA20240108002</t>
+          <t>TEST001</t>
         </is>
       </c>
     </row>

--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260611113056910788fe5bd5ec6ae2476785765548ec59ff95</t>
+          <t>202606111218077261270a11bbaeb2ff435986092dd1995ecac1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,135 +496,33 @@
           <t>北京银行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>1090312345678901</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>北京XX科技有限公司</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2024-01-05</t>
+          <t>6222021234567890</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-50000</v>
+        <v>-1000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>采购付款</t>
+          <t>测试交易</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>供应商A公司</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1500000</v>
+        <v>5000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>BJ20240105001</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20260611113056910982d11b53259d0c4061a0260aaa6b2b82c0</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>北京银行</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1090312345678901</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>北京XX科技有限公司</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>销售收款</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>客户B公司</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1580000</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>BJ20240110002</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026061111305702175435f5906dcf714198850584d2215db29b</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>北京银行</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>01090312345678901</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>北京XX科技有限公司</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>测试收款</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>测试公司</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>10000</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>TEST001</t>
+          <t>TXN001</t>
         </is>
       </c>
     </row>

--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,10 +498,8 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>6222021234567890</t>
-        </is>
+      <c r="E2" t="n">
+        <v>6222021234567890</v>
       </c>
       <c r="F2" t="n">
         <v>-1000</v>
@@ -523,6 +521,194 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>TXN001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260611125348827560ff92e1a3e0854df7860994fe87320045</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京银行</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1090312345678901</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-01-05</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>采购付款</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>供应商A公司</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BJ20240105001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026061112534882759460b84ad5f1144a0e82322fcb513487e3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>北京银行</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1090312345678901</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>客户B公司</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>BJ20240110002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260611125348952966cc5197088fc542bab6d8b704882a4cdc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>东亚银行</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>38812345678</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>上海YY贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2024-01-03</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>-20000</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>向 张三 付款-货款</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>向 张三 付款-货款</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>480000</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>EA20240103001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026061112534895298796951a04b5d14688a22d5ca7e7ae4405</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>东亚银行</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>38812345678</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>上海YY贸易有限公司</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2024-01-08</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>收到 李四 汇款-服务费</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>收到 李四 汇款-服务费</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>515000</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>EA20240108002</t>
         </is>
       </c>
     </row>

--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202606111218077261270a11bbaeb2ff435986092dd1995ecac1</t>
+          <t>202606111419154130464713fc68c5b447cd834de9a05080df93</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,8 +498,10 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>6222021234567890</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6222021234567890</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>-1000</v>
@@ -521,194 +523,6 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>TXN001</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>20260611125348827560ff92e1a3e0854df7860994fe87320045</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>北京银行</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1090312345678901</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>北京XX科技有限公司</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2024-01-05</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>-50000</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>采购付款</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>供应商A公司</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>BJ20240105001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026061112534882759460b84ad5f1144a0e82322fcb513487e3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>北京银行</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>1090312345678901</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>北京XX科技有限公司</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>80000</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>销售收款</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>客户B公司</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>1580000</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>BJ20240110002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20260611125348952966cc5197088fc542bab6d8b704882a4cdc</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>东亚银行</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>38812345678</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>上海YY贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2024-01-03</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>-20000</v>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>向 张三 付款-货款</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>向 张三 付款-货款</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>480000</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>EA20240103001</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026061112534895298796951a04b5d14688a22d5ca7e7ae4405</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>东亚银行</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>38812345678</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>上海YY贸易有限公司</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2024-01-08</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>35000</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>收到 李四 汇款-服务费</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>收到 李四 汇款-服务费</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>515000</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>EA20240108002</t>
         </is>
       </c>
     </row>

--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,21 @@
           <t>交易流水号</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>异常标记</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>异常详情</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>202606111419154130464713fc68c5b447cd834de9a05080df93</t>
+          <t>20260615094310775915e3db26c3f2d04ecd90dd544187d07c35</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -496,35 +506,96 @@
           <t>北京银行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>01090312345678901</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>6222021234567890</t>
+          <t>2024-01-05</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>-1000</v>
+        <v>-50000</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>测试交易</t>
+          <t>采购付款</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>供应商A公司</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>5000</v>
+        <v>1500000</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>TXN001</t>
-        </is>
-      </c>
+          <t>BJ20240105001</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260615094310776032059255e9c6d540cd90b2e5303a34903d</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>北京银行</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>01090312345678901</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>北京XX科技有限公司</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2024-01-10</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>销售收款</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>客户B公司</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1580000</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>BJ20240110002</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/银行流水总表.xlsx
+++ b/backend/银行流水总表.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,11 +494,26 @@
           <t>异常详情</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>来源文件名</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>来源相对路径</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260615094310775915e3db26c3f2d04ecd90dd544187d07c35</t>
+          <t>20260615095122425442a1ab4bbf392143c5bd1ca8a50c70faa9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -545,11 +560,14 @@
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260615094310776032059255e9c6d540cd90b2e5303a34903d</t>
+          <t>20260615095122425701b7148cf2e35240c1be0aa4b7ff5aea7b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -596,6 +614,9 @@
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
